--- a/configs/monster.xlsx
+++ b/configs/monster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DreamCC\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CD1D84-8BC2-41C9-A189-540E4BE5CEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52548144-FA39-4BC1-8402-8DB62036A500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27924" yWindow="1764" windowWidth="23040" windowHeight="13572" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster" sheetId="1" r:id="rId1"/>
@@ -24,71 +24,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Greggj</author>
-  </authors>
-  <commentList>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{59500331-56E8-422B-AF67-B393722B3B73}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Greggj:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-每秒移动速度</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{633F4EC5-76B5-4835-BADB-001A95B7041E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Greggj:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-0 物理
-2 魔法</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -98,21 +35,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>armor</t>
-  </si>
-  <si>
-    <t>number</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[number]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -165,18 +87,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>armor_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>护甲类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>护甲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>anchor</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -189,14 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>speed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动速度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>life</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -235,13 +137,25 @@
   </si>
   <si>
     <t>0.2,0.2</t>
+  </si>
+  <si>
+    <t>attr_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性集合ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,21 +169,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -576,196 +475,162 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="16.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" customWidth="1"/>
-    <col min="12" max="13" width="15" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9" style="1"/>
-    <col min="15" max="15" width="19.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="1" max="9" width="16.109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="1"/>
+    <col min="12" max="12" width="19.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>1</v>
-      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="1">
-        <v>50</v>
+        <v>28</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="J5" s="1">
-        <v>60</v>
-      </c>
-      <c r="M5" s="1">
         <v>1</v>
       </c>
-      <c r="O5" s="1">
+      <c r="L5" s="1">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>